--- a/Praktek Komputer - Spreadsheet/Praktikum UAS/HKB - UAS Praktik ADM Layanan.xlsx
+++ b/Praktek Komputer - Spreadsheet/Praktikum UAS/HKB - UAS Praktik ADM Layanan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY Labs\OpenLearning\Praktek Komputer - Spreadsheet\Praktikum UAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39CD0C9-32A6-420A-9F45-7B47DE970548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C9C97D-79CB-4643-8563-D56BB73E07A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Deskripsi &amp; Petunjuk" sheetId="4" r:id="rId1"/>
@@ -449,7 +449,155 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Kode HKD berakhiran </t>
+      <t xml:space="preserve">Berakhiran </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>05 → 15% biaya layanan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Berakhiran </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>07 → 7% biaya layanan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selain itu → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1% biaya layanan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Status Kepegawaian </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tetap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Rp1.200.000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Status Kepegawaian </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Honor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Rp800.000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Status Kepegawaian </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tetap ATAU Status Perkawinan Kawin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">→ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>35% dari Insentif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selain itu → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20% dari Insentif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kode HKB berakhiran </t>
     </r>
     <r>
       <rPr>
@@ -461,154 +609,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>01 → 10% biaya layanan</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Berakhiran </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>05 → 15% biaya layanan</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Berakhiran </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>07 → 7% biaya layanan</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Selain itu → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1% biaya layanan</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Status Kepegawaian </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tetap</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Rp1.200.000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Status Kepegawaian </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Honor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → Rp800.000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Status Kepegawaian </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tetap ATAU Status Perkawinan Kawin</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">→ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>35% dari Insentif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Selain itu → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>20% dari Insentif</t>
     </r>
   </si>
 </sst>
@@ -1020,48 +1020,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1081,8 +1039,50 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1786,8 +1786,8 @@
       <c r="E14" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
       <c r="H14" s="13"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20"/>
@@ -1798,8 +1798,8 @@
       <c r="E15" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="20"/>
@@ -1810,10 +1810,10 @@
       <c r="E16" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="47"/>
+      <c r="G16" s="54"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -1965,45 +1965,45 @@
       <c r="M5" s="25"/>
     </row>
     <row r="6" spans="1:17" s="23" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58" t="s">
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="58"/>
-      <c r="G6" s="51" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="52"/>
-      <c r="I6" s="58" t="s">
+      <c r="H6" s="62"/>
+      <c r="I6" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="58" t="s">
+      <c r="J6" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="58" t="s">
+      <c r="K6" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="58" t="s">
+      <c r="L6" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="M6" s="58" t="s">
+      <c r="M6" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="O6" s="67" t="s">
+      <c r="O6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
     </row>
     <row r="7" spans="1:17" s="23" customFormat="1" ht="25.8" customHeight="1" thickBot="1">
-      <c r="A7" s="59"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="31" t="s">
         <v>28</v>
       </c>
@@ -2025,14 +2025,14 @@
       <c r="H7" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="67"/>
-      <c r="Q7" s="67"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="57"/>
+      <c r="Q7" s="57"/>
     </row>
     <row r="8" spans="1:17" ht="16.2" thickTop="1">
       <c r="A8" s="32">
@@ -2054,9 +2054,9 @@
       <c r="K8" s="33"/>
       <c r="L8" s="33"/>
       <c r="M8" s="33"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
     </row>
     <row r="9" spans="1:17" ht="15.6">
       <c r="A9" s="34">
@@ -2104,11 +2104,11 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
-      <c r="O10" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
+      <c r="O10" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
     </row>
     <row r="11" spans="1:17" ht="15.6">
       <c r="A11" s="34">
@@ -2130,11 +2130,11 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="O11" s="64" t="s">
-        <v>98</v>
-      </c>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
+      <c r="O11" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
     </row>
     <row r="12" spans="1:17" ht="15.6">
       <c r="A12" s="34">
@@ -2156,11 +2156,11 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="O12" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="P12" s="63"/>
-      <c r="Q12" s="63"/>
+      <c r="O12" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
     </row>
     <row r="13" spans="1:17" ht="15.6">
       <c r="A13" s="34">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="62"/>
+      <c r="E13" s="48"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -2180,11 +2180,11 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
-      <c r="O13" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="P13" s="63"/>
-      <c r="Q13" s="63"/>
+      <c r="O13" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
     </row>
     <row r="14" spans="1:17" ht="15.6">
       <c r="A14" s="34">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="62"/>
+      <c r="E14" s="48"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="62"/>
+      <c r="E15" s="48"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -2228,11 +2228,11 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="O15" s="64" t="s">
-        <v>101</v>
-      </c>
-      <c r="P15" s="63"/>
-      <c r="Q15" s="63"/>
+      <c r="O15" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
     </row>
     <row r="16" spans="1:17" ht="15.6">
       <c r="A16" s="34">
@@ -2254,11 +2254,11 @@
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
-      <c r="O16" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
+      <c r="O16" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
     </row>
     <row r="17" spans="1:17" ht="15.6">
       <c r="A17" s="34">
@@ -2306,11 +2306,11 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="O18" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="63"/>
+      <c r="O18" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="49"/>
     </row>
     <row r="19" spans="1:17" ht="15.6">
       <c r="A19" s="34">
@@ -2332,11 +2332,11 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
-      <c r="O19" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="63"/>
+      <c r="O19" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
     </row>
     <row r="20" spans="1:17" ht="15.6">
       <c r="A20" s="34">
@@ -2358,11 +2358,11 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
-      <c r="O20" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
+      <c r="O20" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
     </row>
     <row r="21" spans="1:17" ht="15.6">
       <c r="A21" s="34">
@@ -2410,11 +2410,11 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
-      <c r="O22" s="65" t="s">
+      <c r="O22" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="49"/>
     </row>
     <row r="23" spans="1:17" ht="15.6">
       <c r="A23" s="34">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="62"/>
+      <c r="E24" s="48"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -2460,11 +2460,11 @@
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
-      <c r="O24" s="66" t="s">
+      <c r="O24" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="49"/>
     </row>
     <row r="25" spans="1:17" ht="15.6">
       <c r="A25" s="34">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="62"/>
+      <c r="E25" s="48"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
@@ -2484,9 +2484,9 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="49"/>
     </row>
     <row r="26" spans="1:17" ht="15.6">
       <c r="A26" s="34">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="62"/>
+      <c r="E26" s="48"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -2533,16 +2533,16 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="16.2" thickTop="1">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="55"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="65"/>
       <c r="I28" s="44"/>
       <c r="J28" s="44"/>
       <c r="K28" s="44"/>
@@ -2559,16 +2559,16 @@
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.6">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="50"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="60"/>
       <c r="I29" s="45"/>
       <c r="J29" s="45"/>
       <c r="K29" s="45"/>
@@ -2583,16 +2583,16 @@
       <c r="Q29" s="30"/>
     </row>
     <row r="30" spans="1:17" ht="15.6">
-      <c r="A30" s="57" t="s">
+      <c r="A30" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="50"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="60"/>
       <c r="I30" s="45"/>
       <c r="J30" s="45"/>
       <c r="K30" s="45"/>
@@ -2607,16 +2607,16 @@
       <c r="Q30" s="30"/>
     </row>
     <row r="31" spans="1:17" ht="15.6">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="50"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="45"/>
       <c r="J31" s="45"/>
       <c r="K31" s="45"/>
@@ -2631,21 +2631,21 @@
       <c r="Q31" s="30"/>
     </row>
     <row r="32" spans="1:17" ht="15.6">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="50"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="60"/>
       <c r="O32" s="8">
         <v>2516004</v>
       </c>
@@ -2674,6 +2674,17 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -2681,17 +2692,6 @@
     <mergeCell ref="D32:M32"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="D28:H28"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
   </mergeCells>
@@ -2769,7 +2769,7 @@
       <c r="D4" s="40">
         <v>250000</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="46">
         <v>2516001</v>
       </c>
       <c r="H4" s="8" t="s">
@@ -2899,7 +2899,7 @@
       <c r="D9" s="40">
         <v>350000</v>
       </c>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="47" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="12" t="s">
